--- a/corpus/xlsx/level-095/template.xlsx
+++ b/corpus/xlsx/level-095/template.xlsx
@@ -39,25 +39,25 @@
   <!-- fixture padding 10 -->
   <pkg:definedNames>
     <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange1">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange2">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange3">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange4">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange5">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange6">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange7">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange8">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange9">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 10 -->
-    <pkg:definedName name="ItemRange10">'Report'!$A$40:$D$40</pkg:definedName>
+    <pkg:definedName name="ItemRange1">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange2">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange3">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange4">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange5">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange6">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange7">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange8">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange9">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 10 -->
+    <pkg:definedName name="ItemRange10">'Report'!$A$40:$D$41</pkg:definedName>
     <!-- fixture padding 10 -->
   </pkg:definedNames>
   <!-- fixture padding 10 -->
@@ -68,7 +68,7 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <!-- fixture padding 10 -->
-<pkg:sst xmlns:pkg="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="225">
+<pkg:sst xmlns:pkg="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="226">
   <!-- fixture padding 10 -->
   <pkg:si>
     <!-- fixture padding 10 -->
@@ -264,7 +264,23 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -345,22 +361,6 @@
       </pkg:rPr>
       <!-- fixture padding 10 -->
       <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -412,7 +412,23 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -444,23 +460,23 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">u</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">st</pkg:t>
+      <pkg:t xml:space="preserve">us</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">t</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -524,23 +540,7 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">r</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}}</pkg:t>
+      <pkg:t xml:space="preserve">r}</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -576,7 +576,23 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -657,22 +673,6 @@
       </pkg:rPr>
       <!-- fixture padding 10 -->
       <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -724,7 +724,23 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -821,22 +837,6 @@
       </pkg:rPr>
       <!-- fixture padding 10 -->
       <pkg:t xml:space="preserve">d</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -888,7 +888,23 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -1000,23 +1016,7 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">d</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}}</pkg:t>
+      <pkg:t xml:space="preserve">d}</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -1052,7 +1052,23 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -1164,23 +1180,7 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">l</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}}</pkg:t>
+      <pkg:t xml:space="preserve">l}</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -1568,71 +1568,55 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">#e</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">ac</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">h i</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">te</pkg:t>
+      <pkg:t xml:space="preserve">{</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">d.</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">it</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -1664,23 +1648,39 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}}{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{n</pkg:t>
+      <pkg:t xml:space="preserve">[i</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">]</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.n</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -1712,7 +1712,7 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">e}}</pkg:t>
+      <pkg:t xml:space="preserve">e}</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -1732,55 +1732,103 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">q</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">u</pkg:t>
+      <pkg:t xml:space="preserve">{d</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.i</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">te</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">ms</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">[i</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">].</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">qu</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -1812,71 +1860,23 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">i</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">y</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}}</pkg:t>
+      <pkg:t xml:space="preserve">ti</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">ty}</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -1912,6 +1912,154 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">d.</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">it</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">em</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">s[</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">i</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">].</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">pr</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">ic</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">e}</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+  </pkg:si>
+  <!-- fixture padding 10 -->
+  <pkg:si>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
       <pkg:t xml:space="preserve">{</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
@@ -1928,103 +2076,135 @@
         <!-- fixture padding 10 -->
       </pkg:rPr>
       <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">p</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">r</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">i</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">c</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
-      <!-- fixture padding 10 -->
-    </pkg:r>
-    <!-- fixture padding 10 -->
-    <pkg:r>
-      <!-- fixture padding 10 -->
-      <pkg:rPr>
-        <!-- fixture padding 10 -->
-        <pkg:b/>
-        <!-- fixture padding 10 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 10 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 10 -->
-      </pkg:rPr>
-      <!-- fixture padding 10 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
+      <pkg:t xml:space="preserve">d.</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">it</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">em</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">s[</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">i+</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">1]</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">.n</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">am</pkg:t>
+      <!-- fixture padding 10 -->
+    </pkg:r>
+    <!-- fixture padding 10 -->
+    <pkg:r>
+      <!-- fixture padding 10 -->
+      <pkg:rPr>
+        <!-- fixture padding 10 -->
+        <pkg:b/>
+        <!-- fixture padding 10 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 10 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 10 -->
+      </pkg:rPr>
+      <!-- fixture padding 10 -->
+      <pkg:t xml:space="preserve">e}</pkg:t>
       <!-- fixture padding 10 -->
     </pkg:r>
     <!-- fixture padding 10 -->
@@ -35018,7 +35198,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="1" name="Picture 1" descr="{{image:red}}"/>
+        <xdr:cNvPr id="1" name="Picture 1" descr="{d.red}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -35080,7 +35260,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="2" name="Picture 2" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="2" name="Picture 2" descr="{d.blue}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -35142,7 +35322,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="3" name="Picture 3" descr="{{image:red}}"/>
+        <xdr:cNvPr id="3" name="Picture 3" descr="{d.red}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -35204,7 +35384,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="4" name="Picture 4" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="4" name="Picture 4" descr="{d.blue}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -35266,7 +35446,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="5" name="Picture 5" descr="{{image:red}}"/>
+        <xdr:cNvPr id="5" name="Picture 5" descr="{d.red}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -35328,7 +35508,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="6" name="Picture 6" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="6" name="Picture 6" descr="{d.blue}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -35390,7 +35570,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="7" name="Picture 7" descr="{{image:red}}"/>
+        <xdr:cNvPr id="7" name="Picture 7" descr="{d.red}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -35452,7 +35632,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="8" name="Picture 8" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="8" name="Picture 8" descr="{d.blue}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -35514,7 +35694,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="9" name="Picture 9" descr="{{image:red}}"/>
+        <xdr:cNvPr id="9" name="Picture 9" descr="{d.red}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -35576,7 +35756,7 @@
       <!-- fixture padding 10 -->
       <xdr:nvPicPr>
         <!-- fixture padding 10 -->
-        <xdr:cNvPr id="10" name="Picture 10" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="10" name="Picture 10" descr="{d.blue}"/>
         <!-- fixture padding 10 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 10 -->
@@ -35623,9 +35803,9 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <!-- fixture padding 10 -->
-<pkg:table xmlns:pkg="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Items" displayName="Items" ref="A39:D40" totalsRowShown="0">
+<pkg:table xmlns:pkg="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Items" displayName="Items" ref="A39:D41" totalsRowShown="0">
   <!-- fixture padding 10 -->
-  <pkg:autoFilter ref="A39:D40"/>
+  <pkg:autoFilter ref="A39:D41"/>
   <!-- fixture padding 10 -->
   <pkg:tableColumns count="4">
     <!-- fixture padding 10 -->
@@ -35648,7 +35828,7 @@
 <!-- fixture padding 10 -->
 <pkg:worksheet xmlns:pkg="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <!-- fixture padding 10 -->
-  <pkg:dimension ref="A1:J299"/>
+  <pkg:dimension ref="A1:J300"/>
   <!-- fixture padding 10 -->
   <!-- fixture padding 10 -->
   <pkg:sheetFormatPr defaultRowHeight="15"/>
@@ -36303,33 +36483,33 @@
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="E40" s="0" t="inlineStr">
-        <!-- fixture padding 10 -->
-        <pkg:is>
-          <!-- fixture padding 10 -->
-          <pkg:t xml:space="preserve">{{/each}}</pkg:t>
-          <!-- fixture padding 10 -->
-        </pkg:is>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="100">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A100" s="0" t="s">
+    <pkg:row r="41">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A41" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>14</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="B100" s="0" t="s">
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="101">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A101" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>15</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B101" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C100" s="0">
+      <pkg:c r="C101" s="0">
         <!-- fixture padding 10 -->
         <pkg:v>0</pkg:v>
         <!-- fixture padding 10 -->
@@ -36337,4377 +36517,4377 @@
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="101">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A101" s="0" t="s">
+    <pkg:row r="102">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A102" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>16</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B102" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C102" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>1</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="103">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A103" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>17</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B103" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C103" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="104">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A104" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>18</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B104" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C104" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>3</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="105">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A105" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>19</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B105" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C105" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>4</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="106">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A106" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>20</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B106" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C106" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>5</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="107">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A107" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>21</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B107" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C107" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>6</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="108">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A108" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>22</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B108" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C108" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>7</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="109">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A109" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>23</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B109" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C109" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>8</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="110">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A110" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>24</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B110" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C110" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>9</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="111">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A111" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>25</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B111" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C111" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>10</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="112">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A112" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>26</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B112" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C112" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>11</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="113">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A113" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>27</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B113" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C113" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>12</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="114">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A114" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>28</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B114" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C114" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>13</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="115">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A115" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>29</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B115" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C115" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>14</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="116">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A116" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>30</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B116" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>2</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="C116" s="0">
         <!-- fixture padding 10 -->
         <pkg:v>15</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="B101" s="0" t="s">
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="117">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A117" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>31</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B117" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C101" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>1</pkg:v>
+      <pkg:c r="C117" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>16</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="102">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A102" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>16</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B102" s="0" t="s">
+    <pkg:row r="118">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A118" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>32</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B118" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C102" s="0">
+      <pkg:c r="C118" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>17</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+    </pkg:row>
+    <!-- fixture padding 10 -->
+    <pkg:row r="119">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A119" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>33</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B119" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
+      <pkg:c r="C119" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>18</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="103">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A103" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>17</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B103" s="0" t="s">
+    <pkg:row r="120">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A120" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>34</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B120" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C103" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>3</pkg:v>
+      <pkg:c r="C120" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>19</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="104">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A104" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>18</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B104" s="0" t="s">
+    <pkg:row r="121">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A121" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>35</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B121" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C104" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>4</pkg:v>
+      <pkg:c r="C121" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>20</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="105">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A105" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>19</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B105" s="0" t="s">
+    <pkg:row r="122">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A122" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>36</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B122" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C105" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>5</pkg:v>
+      <pkg:c r="C122" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>21</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="106">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A106" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>20</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B106" s="0" t="s">
+    <pkg:row r="123">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A123" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>37</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B123" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C106" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>6</pkg:v>
+      <pkg:c r="C123" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>22</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="107">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A107" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>21</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B107" s="0" t="s">
+    <pkg:row r="124">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A124" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>38</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B124" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C107" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>7</pkg:v>
+      <pkg:c r="C124" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>23</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="108">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A108" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>22</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B108" s="0" t="s">
+    <pkg:row r="125">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A125" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>39</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B125" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C108" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>8</pkg:v>
+      <pkg:c r="C125" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>24</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="109">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A109" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>23</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B109" s="0" t="s">
+    <pkg:row r="126">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A126" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>40</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B126" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C109" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>9</pkg:v>
+      <pkg:c r="C126" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>25</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="110">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A110" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>24</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B110" s="0" t="s">
+    <pkg:row r="127">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A127" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>41</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B127" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C110" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>10</pkg:v>
+      <pkg:c r="C127" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>26</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="111">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A111" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>25</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B111" s="0" t="s">
+    <pkg:row r="128">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A128" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>42</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B128" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C111" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>11</pkg:v>
+      <pkg:c r="C128" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>27</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="112">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A112" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>26</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B112" s="0" t="s">
+    <pkg:row r="129">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A129" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>43</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B129" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C112" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>12</pkg:v>
+      <pkg:c r="C129" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>28</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="113">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A113" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>27</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B113" s="0" t="s">
+    <pkg:row r="130">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A130" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>44</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B130" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C113" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>13</pkg:v>
+      <pkg:c r="C130" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>29</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="114">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A114" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>28</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B114" s="0" t="s">
+    <pkg:row r="131">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A131" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>45</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B131" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C114" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>14</pkg:v>
+      <pkg:c r="C131" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>30</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="115">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A115" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>29</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B115" s="0" t="s">
+    <pkg:row r="132">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A132" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>46</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B132" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C115" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>15</pkg:v>
+      <pkg:c r="C132" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>31</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="116">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A116" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>30</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B116" s="0" t="s">
+    <pkg:row r="133">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A133" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>47</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B133" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C116" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>16</pkg:v>
+      <pkg:c r="C133" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>32</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="117">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A117" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>31</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B117" s="0" t="s">
+    <pkg:row r="134">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A134" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>48</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B134" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C117" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>17</pkg:v>
+      <pkg:c r="C134" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>33</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="118">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A118" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>32</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B118" s="0" t="s">
+    <pkg:row r="135">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A135" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>49</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B135" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C118" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>18</pkg:v>
+      <pkg:c r="C135" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>34</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="119">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A119" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>33</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B119" s="0" t="s">
+    <pkg:row r="136">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A136" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>50</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B136" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C119" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>19</pkg:v>
+      <pkg:c r="C136" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>35</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="120">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A120" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>34</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B120" s="0" t="s">
+    <pkg:row r="137">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A137" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>51</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B137" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C120" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>20</pkg:v>
+      <pkg:c r="C137" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>36</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="121">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A121" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>35</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B121" s="0" t="s">
+    <pkg:row r="138">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A138" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>52</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B138" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C121" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>21</pkg:v>
+      <pkg:c r="C138" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>37</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="122">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A122" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>36</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B122" s="0" t="s">
+    <pkg:row r="139">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A139" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>53</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B139" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C122" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>22</pkg:v>
+      <pkg:c r="C139" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>38</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="123">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A123" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>37</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B123" s="0" t="s">
+    <pkg:row r="140">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A140" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>54</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B140" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C123" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>23</pkg:v>
+      <pkg:c r="C140" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>39</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="124">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A124" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>38</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B124" s="0" t="s">
+    <pkg:row r="141">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A141" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>55</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B141" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C124" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>24</pkg:v>
+      <pkg:c r="C141" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>40</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="125">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A125" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>39</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B125" s="0" t="s">
+    <pkg:row r="142">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A142" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>56</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B142" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C125" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>25</pkg:v>
+      <pkg:c r="C142" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>41</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="126">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A126" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>40</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B126" s="0" t="s">
+    <pkg:row r="143">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A143" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>57</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B143" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C126" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>26</pkg:v>
+      <pkg:c r="C143" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>42</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="127">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A127" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>41</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B127" s="0" t="s">
+    <pkg:row r="144">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A144" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>58</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B144" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C127" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>27</pkg:v>
+      <pkg:c r="C144" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>43</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="128">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A128" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>42</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B128" s="0" t="s">
+    <pkg:row r="145">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A145" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>59</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B145" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C128" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>28</pkg:v>
+      <pkg:c r="C145" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>44</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="129">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A129" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>43</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B129" s="0" t="s">
+    <pkg:row r="146">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A146" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>60</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B146" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C129" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>29</pkg:v>
+      <pkg:c r="C146" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>45</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="130">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A130" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>44</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B130" s="0" t="s">
+    <pkg:row r="147">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A147" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>61</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B147" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C130" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>30</pkg:v>
+      <pkg:c r="C147" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>46</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="131">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A131" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>45</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B131" s="0" t="s">
+    <pkg:row r="148">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A148" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>62</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B148" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C131" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>31</pkg:v>
+      <pkg:c r="C148" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>47</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="132">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A132" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>46</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B132" s="0" t="s">
+    <pkg:row r="149">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A149" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>63</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B149" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C132" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>32</pkg:v>
+      <pkg:c r="C149" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>48</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="133">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A133" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>47</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B133" s="0" t="s">
+    <pkg:row r="150">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A150" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>64</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B150" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C133" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>33</pkg:v>
+      <pkg:c r="C150" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>49</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="134">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A134" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>48</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B134" s="0" t="s">
+    <pkg:row r="151">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A151" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>65</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B151" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C134" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>34</pkg:v>
+      <pkg:c r="C151" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>50</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="135">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A135" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>49</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B135" s="0" t="s">
+    <pkg:row r="152">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A152" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>66</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B152" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C135" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>35</pkg:v>
+      <pkg:c r="C152" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>51</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="136">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A136" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>50</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B136" s="0" t="s">
+    <pkg:row r="153">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A153" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>67</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B153" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C136" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>36</pkg:v>
+      <pkg:c r="C153" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>52</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="137">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A137" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>51</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B137" s="0" t="s">
+    <pkg:row r="154">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A154" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>68</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B154" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C137" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>37</pkg:v>
+      <pkg:c r="C154" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>53</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="138">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A138" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>52</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B138" s="0" t="s">
+    <pkg:row r="155">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A155" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>69</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B155" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C138" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>38</pkg:v>
+      <pkg:c r="C155" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>54</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="139">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A139" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>53</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B139" s="0" t="s">
+    <pkg:row r="156">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A156" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>70</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B156" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C139" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>39</pkg:v>
+      <pkg:c r="C156" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>55</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="140">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A140" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>54</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B140" s="0" t="s">
+    <pkg:row r="157">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A157" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>71</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B157" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C140" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>40</pkg:v>
+      <pkg:c r="C157" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>56</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="141">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A141" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>55</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B141" s="0" t="s">
+    <pkg:row r="158">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A158" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>72</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B158" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C141" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>41</pkg:v>
+      <pkg:c r="C158" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>57</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="142">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A142" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>56</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B142" s="0" t="s">
+    <pkg:row r="159">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A159" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>73</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B159" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C142" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>42</pkg:v>
+      <pkg:c r="C159" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>58</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="143">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A143" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>57</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B143" s="0" t="s">
+    <pkg:row r="160">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A160" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>74</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B160" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C143" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>43</pkg:v>
+      <pkg:c r="C160" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>59</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="144">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A144" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>58</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B144" s="0" t="s">
+    <pkg:row r="161">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A161" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>75</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B161" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C144" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>44</pkg:v>
+      <pkg:c r="C161" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>60</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="145">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A145" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>59</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B145" s="0" t="s">
+    <pkg:row r="162">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A162" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>76</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B162" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C145" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>45</pkg:v>
+      <pkg:c r="C162" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>61</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="146">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A146" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>60</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B146" s="0" t="s">
+    <pkg:row r="163">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A163" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>77</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B163" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C146" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>46</pkg:v>
+      <pkg:c r="C163" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>62</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="147">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A147" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>61</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B147" s="0" t="s">
+    <pkg:row r="164">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A164" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>78</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B164" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C147" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>47</pkg:v>
+      <pkg:c r="C164" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>63</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="148">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A148" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>62</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B148" s="0" t="s">
+    <pkg:row r="165">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A165" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>79</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B165" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C148" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>48</pkg:v>
+      <pkg:c r="C165" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>64</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="149">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A149" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>63</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B149" s="0" t="s">
+    <pkg:row r="166">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A166" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>80</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B166" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C149" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>49</pkg:v>
+      <pkg:c r="C166" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>65</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="150">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A150" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>64</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B150" s="0" t="s">
+    <pkg:row r="167">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A167" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>81</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B167" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C150" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>50</pkg:v>
+      <pkg:c r="C167" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>66</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="151">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A151" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>65</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B151" s="0" t="s">
+    <pkg:row r="168">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A168" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>82</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B168" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C151" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>51</pkg:v>
+      <pkg:c r="C168" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>67</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="152">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A152" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>66</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B152" s="0" t="s">
+    <pkg:row r="169">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A169" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>83</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B169" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C152" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>52</pkg:v>
+      <pkg:c r="C169" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>68</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="153">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A153" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>67</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B153" s="0" t="s">
+    <pkg:row r="170">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A170" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>84</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B170" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C153" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>53</pkg:v>
+      <pkg:c r="C170" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>69</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="154">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A154" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>68</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B154" s="0" t="s">
+    <pkg:row r="171">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A171" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>85</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B171" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C154" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>54</pkg:v>
+      <pkg:c r="C171" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>70</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="155">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A155" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>69</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B155" s="0" t="s">
+    <pkg:row r="172">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A172" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>86</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B172" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C155" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>55</pkg:v>
+      <pkg:c r="C172" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>71</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="156">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A156" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>70</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B156" s="0" t="s">
+    <pkg:row r="173">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A173" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>87</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B173" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C156" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>56</pkg:v>
+      <pkg:c r="C173" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>72</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="157">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A157" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>71</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B157" s="0" t="s">
+    <pkg:row r="174">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A174" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>88</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B174" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C157" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>57</pkg:v>
+      <pkg:c r="C174" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>73</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="158">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A158" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>72</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B158" s="0" t="s">
+    <pkg:row r="175">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A175" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>89</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B175" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C158" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>58</pkg:v>
+      <pkg:c r="C175" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>74</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="159">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A159" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>73</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B159" s="0" t="s">
+    <pkg:row r="176">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A176" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>90</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B176" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C159" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>59</pkg:v>
+      <pkg:c r="C176" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>75</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="160">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A160" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>74</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B160" s="0" t="s">
+    <pkg:row r="177">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A177" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>91</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B177" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C160" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>60</pkg:v>
+      <pkg:c r="C177" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>76</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="161">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A161" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>75</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B161" s="0" t="s">
+    <pkg:row r="178">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A178" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>92</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B178" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C161" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>61</pkg:v>
+      <pkg:c r="C178" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>77</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="162">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A162" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>76</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B162" s="0" t="s">
+    <pkg:row r="179">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A179" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>93</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B179" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C162" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>62</pkg:v>
+      <pkg:c r="C179" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>78</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="163">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A163" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>77</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B163" s="0" t="s">
+    <pkg:row r="180">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A180" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>94</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B180" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C163" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>63</pkg:v>
+      <pkg:c r="C180" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>79</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="164">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A164" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>78</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B164" s="0" t="s">
+    <pkg:row r="181">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A181" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>95</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B181" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C164" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>64</pkg:v>
+      <pkg:c r="C181" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>80</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="165">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A165" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>79</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B165" s="0" t="s">
+    <pkg:row r="182">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A182" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>96</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B182" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C165" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>65</pkg:v>
+      <pkg:c r="C182" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>81</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="166">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A166" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>80</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B166" s="0" t="s">
+    <pkg:row r="183">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A183" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>97</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B183" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C166" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>66</pkg:v>
+      <pkg:c r="C183" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>82</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="167">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A167" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>81</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B167" s="0" t="s">
+    <pkg:row r="184">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A184" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>98</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B184" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C167" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>67</pkg:v>
+      <pkg:c r="C184" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>83</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="168">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A168" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>82</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B168" s="0" t="s">
+    <pkg:row r="185">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A185" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>99</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B185" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C168" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>68</pkg:v>
+      <pkg:c r="C185" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>84</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="169">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A169" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>83</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B169" s="0" t="s">
+    <pkg:row r="186">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A186" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>100</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B186" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C169" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>69</pkg:v>
+      <pkg:c r="C186" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>85</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="170">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A170" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>84</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B170" s="0" t="s">
+    <pkg:row r="187">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A187" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>101</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B187" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C170" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>70</pkg:v>
+      <pkg:c r="C187" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>86</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="171">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A171" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>85</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B171" s="0" t="s">
+    <pkg:row r="188">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A188" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>102</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B188" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C171" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>71</pkg:v>
+      <pkg:c r="C188" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>87</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="172">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A172" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>86</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B172" s="0" t="s">
+    <pkg:row r="189">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A189" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>103</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B189" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C172" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>72</pkg:v>
+      <pkg:c r="C189" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>88</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="173">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A173" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>87</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B173" s="0" t="s">
+    <pkg:row r="190">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A190" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>104</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B190" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C173" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>73</pkg:v>
+      <pkg:c r="C190" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>89</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="174">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A174" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>88</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B174" s="0" t="s">
+    <pkg:row r="191">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A191" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>105</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B191" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C174" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>74</pkg:v>
+      <pkg:c r="C191" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>90</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="175">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A175" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>89</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B175" s="0" t="s">
+    <pkg:row r="192">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A192" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>106</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B192" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C175" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>75</pkg:v>
+      <pkg:c r="C192" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>91</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="176">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A176" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>90</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B176" s="0" t="s">
+    <pkg:row r="193">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A193" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>107</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B193" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C176" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>76</pkg:v>
+      <pkg:c r="C193" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>92</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="177">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A177" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>91</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B177" s="0" t="s">
+    <pkg:row r="194">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A194" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>108</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B194" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C177" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>77</pkg:v>
+      <pkg:c r="C194" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>93</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="178">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A178" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>92</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B178" s="0" t="s">
+    <pkg:row r="195">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A195" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>109</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B195" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C178" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>78</pkg:v>
+      <pkg:c r="C195" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>94</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="179">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A179" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>93</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B179" s="0" t="s">
+    <pkg:row r="196">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A196" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>110</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B196" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C179" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>79</pkg:v>
+      <pkg:c r="C196" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>95</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="180">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A180" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>94</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B180" s="0" t="s">
+    <pkg:row r="197">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A197" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>111</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B197" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C180" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>80</pkg:v>
+      <pkg:c r="C197" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>96</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="181">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A181" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>95</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B181" s="0" t="s">
+    <pkg:row r="198">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A198" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>112</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B198" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C181" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>81</pkg:v>
+      <pkg:c r="C198" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>97</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="182">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A182" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>96</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B182" s="0" t="s">
+    <pkg:row r="199">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A199" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>113</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B199" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C182" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>82</pkg:v>
+      <pkg:c r="C199" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>98</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="183">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A183" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>97</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B183" s="0" t="s">
+    <pkg:row r="200">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A200" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>114</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B200" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C183" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>83</pkg:v>
+      <pkg:c r="C200" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>99</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="184">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A184" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>98</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B184" s="0" t="s">
+    <pkg:row r="201">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A201" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>115</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B201" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C184" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>84</pkg:v>
+      <pkg:c r="C201" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>100</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="185">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A185" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>99</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B185" s="0" t="s">
+    <pkg:row r="202">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A202" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>116</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B202" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C185" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>85</pkg:v>
+      <pkg:c r="C202" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>101</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="186">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A186" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>100</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B186" s="0" t="s">
+    <pkg:row r="203">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A203" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>117</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B203" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C186" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>86</pkg:v>
+      <pkg:c r="C203" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>102</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="187">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A187" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>101</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B187" s="0" t="s">
+    <pkg:row r="204">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A204" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>118</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B204" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C187" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>87</pkg:v>
+      <pkg:c r="C204" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>103</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="188">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A188" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>102</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B188" s="0" t="s">
+    <pkg:row r="205">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A205" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>119</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B205" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C188" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>88</pkg:v>
+      <pkg:c r="C205" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>104</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="189">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A189" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>103</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B189" s="0" t="s">
+    <pkg:row r="206">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A206" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>120</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B206" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C189" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>89</pkg:v>
+      <pkg:c r="C206" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>105</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="190">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A190" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>104</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B190" s="0" t="s">
+    <pkg:row r="207">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A207" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>121</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B207" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C190" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>90</pkg:v>
+      <pkg:c r="C207" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>106</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="191">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A191" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>105</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B191" s="0" t="s">
+    <pkg:row r="208">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A208" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>122</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B208" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C191" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>91</pkg:v>
+      <pkg:c r="C208" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>107</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="192">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A192" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>106</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B192" s="0" t="s">
+    <pkg:row r="209">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A209" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>123</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B209" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C192" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>92</pkg:v>
+      <pkg:c r="C209" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>108</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="193">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A193" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>107</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B193" s="0" t="s">
+    <pkg:row r="210">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A210" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>124</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B210" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C193" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>93</pkg:v>
+      <pkg:c r="C210" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>109</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="194">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A194" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>108</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B194" s="0" t="s">
+    <pkg:row r="211">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A211" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>125</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B211" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C194" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>94</pkg:v>
+      <pkg:c r="C211" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>110</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="195">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A195" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>109</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B195" s="0" t="s">
+    <pkg:row r="212">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A212" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>126</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B212" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C195" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>95</pkg:v>
+      <pkg:c r="C212" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>111</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="196">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A196" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>110</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B196" s="0" t="s">
+    <pkg:row r="213">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A213" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>127</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B213" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C196" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>96</pkg:v>
+      <pkg:c r="C213" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>112</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="197">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A197" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>111</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B197" s="0" t="s">
+    <pkg:row r="214">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A214" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>128</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B214" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C197" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>97</pkg:v>
+      <pkg:c r="C214" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>113</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="198">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A198" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>112</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B198" s="0" t="s">
+    <pkg:row r="215">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A215" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>129</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B215" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C198" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>98</pkg:v>
+      <pkg:c r="C215" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>114</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="199">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A199" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>113</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B199" s="0" t="s">
+    <pkg:row r="216">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A216" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>130</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B216" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C199" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>99</pkg:v>
+      <pkg:c r="C216" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>115</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="200">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A200" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>114</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B200" s="0" t="s">
+    <pkg:row r="217">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A217" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>131</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B217" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C200" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>100</pkg:v>
+      <pkg:c r="C217" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>116</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="201">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A201" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>115</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B201" s="0" t="s">
+    <pkg:row r="218">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A218" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>132</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B218" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C201" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>101</pkg:v>
+      <pkg:c r="C218" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>117</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="202">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A202" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>116</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B202" s="0" t="s">
+    <pkg:row r="219">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A219" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>133</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B219" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C202" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>102</pkg:v>
+      <pkg:c r="C219" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>118</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="203">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A203" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>117</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B203" s="0" t="s">
+    <pkg:row r="220">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A220" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>134</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B220" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C203" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>103</pkg:v>
+      <pkg:c r="C220" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>119</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="204">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A204" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>118</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B204" s="0" t="s">
+    <pkg:row r="221">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A221" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>135</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B221" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C204" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>104</pkg:v>
+      <pkg:c r="C221" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>120</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="205">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A205" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>119</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B205" s="0" t="s">
+    <pkg:row r="222">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A222" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>136</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B222" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C205" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>105</pkg:v>
+      <pkg:c r="C222" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>121</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="206">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A206" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>120</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B206" s="0" t="s">
+    <pkg:row r="223">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A223" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>137</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B223" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C206" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>106</pkg:v>
+      <pkg:c r="C223" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>122</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="207">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A207" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>121</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B207" s="0" t="s">
+    <pkg:row r="224">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A224" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>138</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B224" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C207" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>107</pkg:v>
+      <pkg:c r="C224" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>123</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="208">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A208" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>122</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B208" s="0" t="s">
+    <pkg:row r="225">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A225" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>139</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B225" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C208" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>108</pkg:v>
+      <pkg:c r="C225" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>124</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="209">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A209" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>123</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B209" s="0" t="s">
+    <pkg:row r="226">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A226" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>140</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B226" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C209" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>109</pkg:v>
+      <pkg:c r="C226" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>125</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="210">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A210" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>124</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B210" s="0" t="s">
+    <pkg:row r="227">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A227" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>141</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B227" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C210" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>110</pkg:v>
+      <pkg:c r="C227" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>126</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="211">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A211" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>125</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B211" s="0" t="s">
+    <pkg:row r="228">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A228" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>142</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B228" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C211" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>111</pkg:v>
+      <pkg:c r="C228" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>127</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="212">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A212" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>126</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B212" s="0" t="s">
+    <pkg:row r="229">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A229" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>143</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B229" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C212" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>112</pkg:v>
+      <pkg:c r="C229" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>128</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="213">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A213" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>127</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B213" s="0" t="s">
+    <pkg:row r="230">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A230" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>144</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B230" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C213" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>113</pkg:v>
+      <pkg:c r="C230" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>129</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="214">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A214" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>128</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B214" s="0" t="s">
+    <pkg:row r="231">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A231" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>145</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B231" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C214" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>114</pkg:v>
+      <pkg:c r="C231" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>130</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="215">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A215" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>129</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B215" s="0" t="s">
+    <pkg:row r="232">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A232" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>146</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B232" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C215" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>115</pkg:v>
+      <pkg:c r="C232" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>131</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="216">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A216" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>130</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B216" s="0" t="s">
+    <pkg:row r="233">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A233" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>147</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B233" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C216" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>116</pkg:v>
+      <pkg:c r="C233" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>132</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="217">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A217" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>131</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B217" s="0" t="s">
+    <pkg:row r="234">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A234" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>148</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B234" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C217" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>117</pkg:v>
+      <pkg:c r="C234" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>133</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="218">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A218" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>132</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B218" s="0" t="s">
+    <pkg:row r="235">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A235" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>149</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B235" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C218" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>118</pkg:v>
+      <pkg:c r="C235" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>134</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="219">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A219" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>133</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B219" s="0" t="s">
+    <pkg:row r="236">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A236" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>150</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B236" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C219" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>119</pkg:v>
+      <pkg:c r="C236" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>135</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="220">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A220" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>134</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B220" s="0" t="s">
+    <pkg:row r="237">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A237" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>151</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B237" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C220" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>120</pkg:v>
+      <pkg:c r="C237" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>136</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="221">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A221" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>135</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B221" s="0" t="s">
+    <pkg:row r="238">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A238" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>152</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B238" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C221" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>121</pkg:v>
+      <pkg:c r="C238" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>137</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="222">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A222" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>136</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B222" s="0" t="s">
+    <pkg:row r="239">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A239" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>153</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B239" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C222" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>122</pkg:v>
+      <pkg:c r="C239" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>138</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="223">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A223" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>137</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B223" s="0" t="s">
+    <pkg:row r="240">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A240" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>154</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B240" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C223" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>123</pkg:v>
+      <pkg:c r="C240" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>139</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="224">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A224" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>138</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B224" s="0" t="s">
+    <pkg:row r="241">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A241" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>155</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B241" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C224" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>124</pkg:v>
+      <pkg:c r="C241" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>140</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="225">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A225" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>139</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B225" s="0" t="s">
+    <pkg:row r="242">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A242" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>156</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B242" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C225" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>125</pkg:v>
+      <pkg:c r="C242" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>141</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="226">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A226" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>140</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B226" s="0" t="s">
+    <pkg:row r="243">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A243" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>157</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B243" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C226" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>126</pkg:v>
+      <pkg:c r="C243" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>142</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="227">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A227" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>141</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B227" s="0" t="s">
+    <pkg:row r="244">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A244" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>158</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B244" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C227" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>127</pkg:v>
+      <pkg:c r="C244" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>143</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="228">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A228" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>142</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B228" s="0" t="s">
+    <pkg:row r="245">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A245" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>159</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B245" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C228" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>128</pkg:v>
+      <pkg:c r="C245" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>144</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="229">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A229" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>143</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B229" s="0" t="s">
+    <pkg:row r="246">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A246" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>160</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B246" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C229" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>129</pkg:v>
+      <pkg:c r="C246" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>145</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="230">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A230" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>144</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B230" s="0" t="s">
+    <pkg:row r="247">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A247" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>161</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B247" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C230" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>130</pkg:v>
+      <pkg:c r="C247" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>146</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="231">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A231" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>145</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B231" s="0" t="s">
+    <pkg:row r="248">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A248" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>162</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B248" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C231" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>131</pkg:v>
+      <pkg:c r="C248" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>147</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="232">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A232" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>146</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B232" s="0" t="s">
+    <pkg:row r="249">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A249" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>163</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B249" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C232" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>132</pkg:v>
+      <pkg:c r="C249" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>148</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="233">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A233" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>147</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B233" s="0" t="s">
+    <pkg:row r="250">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A250" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>164</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B250" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C233" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>133</pkg:v>
+      <pkg:c r="C250" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>149</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="234">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A234" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>148</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B234" s="0" t="s">
+    <pkg:row r="251">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A251" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>165</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B251" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C234" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>134</pkg:v>
+      <pkg:c r="C251" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>150</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="235">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A235" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>149</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B235" s="0" t="s">
+    <pkg:row r="252">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A252" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>166</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B252" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C235" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>135</pkg:v>
+      <pkg:c r="C252" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>151</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="236">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A236" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>150</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B236" s="0" t="s">
+    <pkg:row r="253">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A253" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>167</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B253" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C236" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>136</pkg:v>
+      <pkg:c r="C253" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>152</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="237">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A237" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>151</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B237" s="0" t="s">
+    <pkg:row r="254">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A254" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>168</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B254" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C237" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>137</pkg:v>
+      <pkg:c r="C254" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>153</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="238">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A238" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>152</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B238" s="0" t="s">
+    <pkg:row r="255">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A255" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>169</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B255" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C238" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>138</pkg:v>
+      <pkg:c r="C255" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>154</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="239">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A239" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>153</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B239" s="0" t="s">
+    <pkg:row r="256">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A256" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>170</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B256" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C239" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>139</pkg:v>
+      <pkg:c r="C256" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>155</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="240">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A240" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>154</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B240" s="0" t="s">
+    <pkg:row r="257">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A257" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>171</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B257" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C240" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>140</pkg:v>
+      <pkg:c r="C257" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>156</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="241">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A241" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>155</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B241" s="0" t="s">
+    <pkg:row r="258">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A258" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>172</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B258" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C241" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>141</pkg:v>
+      <pkg:c r="C258" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>157</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="242">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A242" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>156</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B242" s="0" t="s">
+    <pkg:row r="259">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A259" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>173</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B259" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C242" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>142</pkg:v>
+      <pkg:c r="C259" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>158</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="243">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A243" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>157</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B243" s="0" t="s">
+    <pkg:row r="260">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A260" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>174</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B260" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C243" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>143</pkg:v>
+      <pkg:c r="C260" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>159</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="244">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A244" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>158</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B244" s="0" t="s">
+    <pkg:row r="261">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A261" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>175</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B261" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C244" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>144</pkg:v>
+      <pkg:c r="C261" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>160</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="245">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A245" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>159</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B245" s="0" t="s">
+    <pkg:row r="262">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A262" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>176</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B262" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C245" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>145</pkg:v>
+      <pkg:c r="C262" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>161</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="246">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A246" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>160</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B246" s="0" t="s">
+    <pkg:row r="263">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A263" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>177</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B263" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C246" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>146</pkg:v>
+      <pkg:c r="C263" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>162</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="247">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A247" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>161</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B247" s="0" t="s">
+    <pkg:row r="264">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A264" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>178</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B264" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C247" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>147</pkg:v>
+      <pkg:c r="C264" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>163</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="248">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A248" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>162</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B248" s="0" t="s">
+    <pkg:row r="265">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A265" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>179</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B265" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C248" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>148</pkg:v>
+      <pkg:c r="C265" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>164</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="249">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A249" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>163</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B249" s="0" t="s">
+    <pkg:row r="266">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A266" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>180</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B266" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C249" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>149</pkg:v>
+      <pkg:c r="C266" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>165</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="250">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A250" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>164</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B250" s="0" t="s">
+    <pkg:row r="267">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A267" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>181</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B267" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C250" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>150</pkg:v>
+      <pkg:c r="C267" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>166</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="251">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A251" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>165</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B251" s="0" t="s">
+    <pkg:row r="268">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A268" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>182</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B268" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C251" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>151</pkg:v>
+      <pkg:c r="C268" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>167</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="252">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A252" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>166</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B252" s="0" t="s">
+    <pkg:row r="269">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A269" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>183</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B269" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C252" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>152</pkg:v>
+      <pkg:c r="C269" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>168</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="253">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A253" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>167</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B253" s="0" t="s">
+    <pkg:row r="270">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A270" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>184</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B270" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C253" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>153</pkg:v>
+      <pkg:c r="C270" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>169</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="254">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A254" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>168</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B254" s="0" t="s">
+    <pkg:row r="271">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A271" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>185</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B271" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C254" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>154</pkg:v>
+      <pkg:c r="C271" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>170</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="255">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A255" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>169</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B255" s="0" t="s">
+    <pkg:row r="272">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A272" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>186</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B272" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C255" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>155</pkg:v>
+      <pkg:c r="C272" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>171</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="256">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A256" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>170</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B256" s="0" t="s">
+    <pkg:row r="273">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A273" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>187</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B273" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C256" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>156</pkg:v>
+      <pkg:c r="C273" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>172</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="257">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A257" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>171</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B257" s="0" t="s">
+    <pkg:row r="274">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A274" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>188</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B274" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C257" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>157</pkg:v>
+      <pkg:c r="C274" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>173</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="258">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A258" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>172</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B258" s="0" t="s">
+    <pkg:row r="275">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A275" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>189</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B275" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C258" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>158</pkg:v>
+      <pkg:c r="C275" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>174</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="259">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A259" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>173</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B259" s="0" t="s">
+    <pkg:row r="276">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A276" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>190</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B276" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C259" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>159</pkg:v>
+      <pkg:c r="C276" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>175</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="260">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A260" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>174</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B260" s="0" t="s">
+    <pkg:row r="277">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A277" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>191</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B277" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C260" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>160</pkg:v>
+      <pkg:c r="C277" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>176</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="261">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A261" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>175</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B261" s="0" t="s">
+    <pkg:row r="278">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A278" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>192</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B278" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C261" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>161</pkg:v>
+      <pkg:c r="C278" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>177</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="262">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A262" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>176</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B262" s="0" t="s">
+    <pkg:row r="279">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A279" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>193</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B279" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C262" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>162</pkg:v>
+      <pkg:c r="C279" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>178</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="263">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A263" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>177</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B263" s="0" t="s">
+    <pkg:row r="280">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A280" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>194</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B280" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C263" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>163</pkg:v>
+      <pkg:c r="C280" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>179</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="264">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A264" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>178</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B264" s="0" t="s">
+    <pkg:row r="281">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A281" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>195</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B281" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C264" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>164</pkg:v>
+      <pkg:c r="C281" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>180</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="265">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A265" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>179</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B265" s="0" t="s">
+    <pkg:row r="282">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A282" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>196</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B282" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C265" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>165</pkg:v>
+      <pkg:c r="C282" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>181</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="266">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A266" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>180</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B266" s="0" t="s">
+    <pkg:row r="283">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A283" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>197</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B283" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C266" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>166</pkg:v>
+      <pkg:c r="C283" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>182</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="267">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A267" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>181</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B267" s="0" t="s">
+    <pkg:row r="284">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A284" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>198</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B284" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C267" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>167</pkg:v>
+      <pkg:c r="C284" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>183</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="268">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A268" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>182</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B268" s="0" t="s">
+    <pkg:row r="285">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A285" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>199</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B285" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C268" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>168</pkg:v>
+      <pkg:c r="C285" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>184</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="269">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A269" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>183</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B269" s="0" t="s">
+    <pkg:row r="286">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A286" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>200</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B286" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C269" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>169</pkg:v>
+      <pkg:c r="C286" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>185</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="270">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A270" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>184</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B270" s="0" t="s">
+    <pkg:row r="287">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A287" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>201</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B287" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C270" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>170</pkg:v>
+      <pkg:c r="C287" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>186</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="271">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A271" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>185</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B271" s="0" t="s">
+    <pkg:row r="288">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A288" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>202</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B288" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C271" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>171</pkg:v>
+      <pkg:c r="C288" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>187</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="272">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A272" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>186</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B272" s="0" t="s">
+    <pkg:row r="289">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A289" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>203</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B289" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C272" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>172</pkg:v>
+      <pkg:c r="C289" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>188</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="273">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A273" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>187</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B273" s="0" t="s">
+    <pkg:row r="290">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A290" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>204</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B290" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C273" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>173</pkg:v>
+      <pkg:c r="C290" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>189</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="274">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A274" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>188</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B274" s="0" t="s">
+    <pkg:row r="291">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A291" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>205</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B291" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C274" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>174</pkg:v>
+      <pkg:c r="C291" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>190</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="275">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A275" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>189</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B275" s="0" t="s">
+    <pkg:row r="292">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A292" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>206</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B292" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C275" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>175</pkg:v>
+      <pkg:c r="C292" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>191</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="276">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A276" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>190</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B276" s="0" t="s">
+    <pkg:row r="293">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A293" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>207</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B293" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C276" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>176</pkg:v>
+      <pkg:c r="C293" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>192</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="277">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A277" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>191</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B277" s="0" t="s">
+    <pkg:row r="294">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A294" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>208</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B294" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C277" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>177</pkg:v>
+      <pkg:c r="C294" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>193</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="278">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A278" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>192</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B278" s="0" t="s">
+    <pkg:row r="295">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A295" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>209</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B295" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C278" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>178</pkg:v>
+      <pkg:c r="C295" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>194</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="279">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A279" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>193</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B279" s="0" t="s">
+    <pkg:row r="296">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A296" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>210</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B296" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C279" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>179</pkg:v>
+      <pkg:c r="C296" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>195</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="280">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A280" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>194</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B280" s="0" t="s">
+    <pkg:row r="297">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A297" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>211</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B297" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C280" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>180</pkg:v>
+      <pkg:c r="C297" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>196</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="281">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A281" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>195</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B281" s="0" t="s">
+    <pkg:row r="298">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A298" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>212</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B298" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C281" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>181</pkg:v>
+      <pkg:c r="C298" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>197</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="282">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A282" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>196</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B282" s="0" t="s">
+    <pkg:row r="299">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A299" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>213</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B299" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C282" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>182</pkg:v>
+      <pkg:c r="C299" s="0">
+        <!-- fixture padding 10 -->
+        <pkg:v>198</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
     </pkg:row>
     <!-- fixture padding 10 -->
-    <pkg:row r="283">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A283" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>197</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B283" s="0" t="s">
+    <pkg:row r="300">
+      <!-- fixture padding 10 -->
+      <pkg:c r="A300" s="0" t="s">
+        <!-- fixture padding 10 -->
+        <pkg:v>214</pkg:v>
+        <!-- fixture padding 10 -->
+      </pkg:c>
+      <!-- fixture padding 10 -->
+      <pkg:c r="B300" s="0" t="s">
         <!-- fixture padding 10 -->
         <pkg:v>2</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
-      <pkg:c r="C283" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>183</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="284">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A284" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>198</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B284" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C284" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>184</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="285">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A285" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>199</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B285" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C285" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>185</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="286">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A286" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>200</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B286" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C286" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>186</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="287">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A287" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>201</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B287" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C287" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>187</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="288">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A288" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>202</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B288" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C288" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>188</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="289">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A289" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>203</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B289" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C289" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>189</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="290">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A290" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>204</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B290" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C290" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>190</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="291">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A291" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>205</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B291" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C291" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>191</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="292">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A292" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>206</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B292" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C292" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>192</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="293">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A293" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>207</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B293" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C293" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>193</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="294">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A294" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>208</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B294" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C294" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>194</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="295">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A295" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>209</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B295" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C295" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>195</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="296">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A296" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>210</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B296" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C296" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>196</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="297">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A297" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>211</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B297" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C297" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>197</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="298">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A298" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>212</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B298" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C298" s="0">
-        <!-- fixture padding 10 -->
-        <pkg:v>198</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-    </pkg:row>
-    <!-- fixture padding 10 -->
-    <pkg:row r="299">
-      <!-- fixture padding 10 -->
-      <pkg:c r="A299" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>213</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="B299" s="0" t="s">
-        <!-- fixture padding 10 -->
-        <pkg:v>2</pkg:v>
-        <!-- fixture padding 10 -->
-      </pkg:c>
-      <!-- fixture padding 10 -->
-      <pkg:c r="C299" s="0">
+      <pkg:c r="C300" s="0">
         <!-- fixture padding 10 -->
         <pkg:v>199</pkg:v>
         <!-- fixture padding 10 -->
@@ -40717,7 +40897,7 @@
     <!-- fixture padding 10 -->
   </pkg:sheetData>
   <!-- fixture padding 10 -->
-  <pkg:autoFilter ref="A39:D40"/>
+  <pkg:autoFilter ref="A39:D41"/>
   <!-- fixture padding 10 -->
   <pkg:mergeCells count="10">
     <!-- fixture padding 10 -->
@@ -40743,7 +40923,7 @@
     <!-- fixture padding 10 -->
   </pkg:mergeCells>
   <!-- fixture padding 10 -->
-  <pkg:conditionalFormatting sqref="B40:B40">
+  <pkg:conditionalFormatting sqref="B40:B41">
     <!-- fixture padding 10 -->
     <pkg:cfRule type="cellIs" priority="1" operator="greaterThan">
       <!-- fixture padding 10 -->
@@ -40755,7 +40935,7 @@
   <!-- fixture padding 10 -->
   <pkg:dataValidations count="8">
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="B40:B40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="B40:B41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -40763,7 +40943,7 @@
       <!-- fixture padding 10 -->
     </pkg:dataValidation>
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="C40:C40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="C40:C41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -40771,7 +40951,7 @@
       <!-- fixture padding 10 -->
     </pkg:dataValidation>
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="D40:D40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="D40:D41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -40779,7 +40959,7 @@
       <!-- fixture padding 10 -->
     </pkg:dataValidation>
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="E40:E40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="E40:E41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -40787,7 +40967,7 @@
       <!-- fixture padding 10 -->
     </pkg:dataValidation>
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="F40:F40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="F40:F41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -40795,7 +40975,7 @@
       <!-- fixture padding 10 -->
     </pkg:dataValidation>
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="G40:G40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="G40:G41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -40803,7 +40983,7 @@
       <!-- fixture padding 10 -->
     </pkg:dataValidation>
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="H40:H40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="H40:H41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -40811,7 +40991,7 @@
       <!-- fixture padding 10 -->
     </pkg:dataValidation>
     <!-- fixture padding 10 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="I40:I40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="I40:I41">
       <!-- fixture padding 10 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 10 -->
@@ -40846,7 +41026,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>222</pkg:v>
+        <pkg:v>223</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -40891,7 +41071,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>223</pkg:v>
+        <pkg:v>224</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -40936,7 +41116,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>224</pkg:v>
+        <pkg:v>225</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -40981,7 +41161,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>214</pkg:v>
+        <pkg:v>215</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -41026,7 +41206,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>215</pkg:v>
+        <pkg:v>216</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -41071,7 +41251,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>216</pkg:v>
+        <pkg:v>217</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -41116,7 +41296,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>217</pkg:v>
+        <pkg:v>218</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -41161,7 +41341,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>218</pkg:v>
+        <pkg:v>219</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -41206,7 +41386,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>219</pkg:v>
+        <pkg:v>220</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -41251,7 +41431,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>220</pkg:v>
+        <pkg:v>221</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
@@ -41296,7 +41476,7 @@
       <!-- fixture padding 10 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 10 -->
-        <pkg:v>221</pkg:v>
+        <pkg:v>222</pkg:v>
         <!-- fixture padding 10 -->
       </pkg:c>
       <!-- fixture padding 10 -->
